--- a/release_forms/029_medical_and_media_release_formmission_trip_participant_manual--release_forms.xlsx
+++ b/release_forms/029_medical_and_media_release_formmission_trip_participant_manual--release_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -880,8 +880,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -909,12 +909,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1,_'value':_'on-campus_events',_'label':_'on-campus_events'}</t>
+          <t>on-campus_events</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1, 'value': 'On-Campus Events', 'label': 'On-Campus Events'}</t>
+          <t>On-Campus Events</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2,_'value':_'off-campus_events',_'label':_'off-campus_events'}</t>
+          <t>off-campus_events</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2, 'value': 'Off-Campus Events', 'label': 'Off-Campus Events'}</t>
+          <t>Off-Campus Events</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_1,_'value':_'i_give_my_consent',_'label':_'i_give_my_consent'}</t>
+          <t>i_give_my_consent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 1, 'value': 'I give my consent', 'label': 'I give my consent'}</t>
+          <t>I give my consent</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_2,_'value':_'i_do_not_give_my_consent',_'label':_'i_do_not_give_my_consent'}</t>
+          <t>i_do_not_give_my_consent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 2, 'value': 'I do not give my consent', 'label': 'I do not give my consent'}</t>
+          <t>I do not give my consent</t>
         </is>
       </c>
     </row>
